--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487552_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487552_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8898</v>
+        <v>11.1819</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3747</v>
+        <v>7.8005</v>
       </c>
       <c r="F2" t="n">
-        <v>3.515</v>
+        <v>3.3814</v>
       </c>
       <c r="G2" t="n">
         <v>6.6553</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.216</v>
+        <v>-0.9238</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3068</v>
+        <v>-0.881</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09089999999999999</v>
+        <v>-0.0428</v>
       </c>
       <c r="V2" t="n">
         <v>2.7086</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0182</v>
+        <v>4.6881</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5886</v>
+        <v>3.2843</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4296</v>
+        <v>1.4039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9112</v>
+        <v>4.228</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9976</v>
+        <v>0.9851</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0864</v>
+        <v>3.2428</v>
       </c>
       <c r="J3" t="n">
-        <v>1.23</v>
+        <v>4.1488</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4684</v>
+        <v>1.1841</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2384</v>
+        <v>2.9648</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3188</v>
+        <v>0.0791</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4708</v>
+        <v>-0.199</v>
       </c>
       <c r="O3" t="n">
-        <v>0.152</v>
+        <v>0.2781</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9377</v>
+        <v>1.9585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3294</v>
+        <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2857</v>
+        <v>-0.2817</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.8646</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9697</v>
+        <v>0.5828</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8837</v>
+        <v>-1.2166</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4344</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5507</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6379</v>
+        <v>4.2093</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0202</v>
+        <v>1.341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6177</v>
+        <v>2.8683</v>
       </c>
       <c r="G4" t="n">
-        <v>4.228</v>
+        <v>0.9112</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9851</v>
+        <v>1.9976</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2428</v>
+        <v>-1.0864</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1488</v>
+        <v>1.23</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1841</v>
+        <v>2.4684</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9648</v>
+        <v>-1.2384</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0791</v>
+        <v>-0.3188</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.199</v>
+        <v>-0.4708</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2781</v>
+        <v>0.152</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9585</v>
+        <v>2.9377</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>3.3294</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3319</v>
+        <v>-0.5233</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1286</v>
+        <v>-0.9316</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7967</v>
+        <v>0.4083</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4344</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0431</v>
+        <v>1.5477</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5738</v>
+        <v>0.8378</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4693</v>
+        <v>0.7099</v>
       </c>
       <c r="G5" t="n">
         <v>1.9276</v>
@@ -844,13 +844,13 @@
         <v>3.3294</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6264</v>
+        <v>-1.1217</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.188</v>
+        <v>-0.924</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4383</v>
+        <v>-0.1978</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2166</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0781</v>
+        <v>-0.0299</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3208</v>
+        <v>-2.509</v>
       </c>
       <c r="F6" t="n">
-        <v>2.399</v>
+        <v>2.4792</v>
       </c>
       <c r="G6" t="n">
         <v>2.821</v>
@@ -922,13 +922,13 @@
         <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7476</v>
+        <v>-0.8556</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.387</v>
+        <v>-0.5752</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3606</v>
+        <v>-0.2804</v>
       </c>
       <c r="V6" t="n">
         <v>0.5507</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4936</v>
+        <v>-0.3318</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2105</v>
+        <v>-1.0488</v>
       </c>
       <c r="F7" t="n">
         <v>0.717</v>
@@ -1000,10 +1000,10 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9375</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4752</v>
+        <v>-0.3135</v>
       </c>
       <c r="U7" t="n">
         <v>-0.4623</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.199</v>
+        <v>-1.7967</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3887</v>
+        <v>-0.227</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8103</v>
+        <v>-1.5697</v>
       </c>
       <c r="G9" t="n">
         <v>0.5666</v>
@@ -1156,13 +1156,13 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7242</v>
+        <v>-0.3219</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4752</v>
+        <v>-0.3135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.249</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4332</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3884</v>
+        <v>-2.2815</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9356</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4528</v>
+        <v>-1.3459</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9436</v>
@@ -1234,13 +1234,13 @@
         <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3445</v>
+        <v>-0.2376</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4158</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0713</v>
+        <v>0.1782</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8837</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0252</v>
+        <v>-3.0322</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4677</v>
+        <v>-3.7153</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4425</v>
+        <v>0.6831</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7039</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3213</v>
+        <v>-0.3283</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2088</v>
+        <v>-0.4564</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1125</v>
+        <v>0.1281</v>
       </c>
       <c r="V11" t="n">
         <v>0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0012</v>
+        <v>13.5952</v>
       </c>
       <c r="E12" t="n">
-        <v>3.682599999999999</v>
+        <v>4.2765</v>
       </c>
       <c r="F12" t="n">
-        <v>9.318700000000002</v>
+        <v>9.318899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>11.1506</v>
@@ -1381,7 +1381,7 @@
         <v>1.4424</v>
       </c>
       <c r="P12" t="n">
-        <v>8.813199999999998</v>
+        <v>8.8132</v>
       </c>
       <c r="Q12" t="n">
         <v>-9.792299999999999</v>
@@ -1390,13 +1390,13 @@
         <v>18.6055</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.9637</v>
+        <v>-5.369599999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.2694</v>
+        <v>-5.6756</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3059000000000002</v>
+        <v>0.3057000000000002</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9987999999999996</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.159</v>
+        <v>3.6974</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2241</v>
+        <v>2.7358</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9349</v>
+        <v>0.9617</v>
       </c>
       <c r="G13" t="n">
         <v>2.708</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4095</v>
+        <v>0.9479</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6422</v>
+        <v>-0.1306</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0518</v>
+        <v>1.0785</v>
       </c>
       <c r="V13" t="n">
         <v>1.2166</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8025</v>
+        <v>1.9156</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5442</v>
+        <v>1.2011</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2583</v>
+        <v>0.7146</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1088</v>
+        <v>0.2389</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.114</v>
+        <v>0.1933</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0052</v>
+        <v>0.0456</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4287</v>
+        <v>0.1629</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4287</v>
+        <v>0.1225</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5375</v>
+        <v>0.076</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5427</v>
+        <v>0.0708</v>
       </c>
       <c r="O14" t="n">
         <v>0.0052</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
         <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3029</v>
+        <v>-0.1689</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1012</v>
+        <v>-0.4158</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4041</v>
+        <v>0.2469</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2166</v>
+        <v>2.4332</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>2.4332</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.782</v>
+        <v>1.7223</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2011</v>
+        <v>1.5442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5809</v>
+        <v>0.1781</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2389</v>
+        <v>-0.1088</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1933</v>
+        <v>-0.114</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0456</v>
+        <v>0.0052</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1629</v>
+        <v>0.4287</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1225</v>
+        <v>0.4287</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.076</v>
+        <v>-0.5375</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0708</v>
+        <v>-0.5427</v>
       </c>
       <c r="O15" t="n">
         <v>0.0052</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3026</v>
+        <v>0.2228</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4158</v>
+        <v>-0.1012</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1132</v>
+        <v>0.3239</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4332</v>
+        <v>1.2166</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4332</v>
+        <v>1.2166</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3655</v>
+        <v>0.9646</v>
       </c>
       <c r="E16" t="n">
         <v>0.3571</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0084</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.249</v>
@@ -1702,13 +1702,13 @@
         <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7249</v>
+        <v>0.3239</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0813</v>
+        <v>0.6803</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6872</v>
+        <v>0.3848</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4439</v>
+        <v>0.0345</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2434</v>
+        <v>0.3503</v>
       </c>
       <c r="G17" t="n">
         <v>0.0358</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4983</v>
+        <v>0.1958</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4205</v>
+        <v>0.0112</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.1847</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8260999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3193</v>
+        <v>-1.8787</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6214</v>
+        <v>-2.3144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3021</v>
+        <v>0.4357</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8354</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3202</v>
+        <v>0.7609</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2858</v>
+        <v>0.0212</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6061</v>
+        <v>0.7397</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6766</v>
+        <v>-3.6674</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1009</v>
+        <v>-2.3055</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5757</v>
+        <v>-1.3619</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7471</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8954</v>
+        <v>0.9046</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4734</v>
+        <v>0.2688</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4219</v>
+        <v>0.6358</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2103</v>
+        <v>-3.694</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7456</v>
+        <v>-1.3363</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4647</v>
+        <v>-2.3577</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6364</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1246</v>
+        <v>0.3917</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5764</v>
+        <v>-0.167</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4518</v>
+        <v>0.5587</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2742</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9094</v>
+        <v>-5.3371</v>
       </c>
       <c r="E22" t="n">
         <v>-4.3067</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6027</v>
+        <v>-1.0304</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4133</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5787</v>
+        <v>1.151</v>
       </c>
       <c r="T22" t="n">
         <v>0.2358</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3428</v>
+        <v>0.9151</v>
       </c>
       <c r="V22" t="n">
         <v>0.2754</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4221</v>
+        <v>-6.849</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3347</v>
+        <v>-4.9487</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0873</v>
+        <v>-1.9002</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1856</v>
@@ -2248,13 +2248,13 @@
         <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>1.661</v>
+        <v>1.2341</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9422</v>
+        <v>0.3282</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7188</v>
+        <v>0.9059</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8260999999999999</v>
@@ -2299,7 +2299,7 @@
         <v>-7.400799999999998</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6249</v>
+        <v>3.624899999999999</v>
       </c>
       <c r="K24" t="n">
         <v>5.0672</v>
@@ -2326,13 +2326,13 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>5.963699999999999</v>
+        <v>5.9638</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3059000000000002</v>
+        <v>-0.3058000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>6.269600000000001</v>
+        <v>6.2695</v>
       </c>
       <c r="V24" t="n">
         <v>0.9987999999999996</v>
